--- a/infra/NEGOCIO.xlsx
+++ b/infra/NEGOCIO.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>Key</t>
   </si>
@@ -69,6 +69,9 @@
     <t>Fecha Venta</t>
   </si>
   <si>
+    <t>Requiere Reparación</t>
+  </si>
+  <si>
     <t>PROD-001</t>
   </si>
   <si>
@@ -115,6 +118,9 @@
   </si>
   <si>
     <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>PROD-002</t>
@@ -219,7 +225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -277,117 +283,126 @@
       <c r="R1" t="s" s="0">
         <v>17</v>
       </c>
+      <c r="S1" t="s" s="0">
+        <v>18</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R2" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="S2" t="s" s="0">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="O3" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="P3" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="Q3" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="R3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="S3" t="s" s="0">
         <v>35</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="N3" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="O3" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="P3" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="Q3" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="R3" t="s" s="0">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -402,35 +417,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/infra/NEGOCIO.xlsx
+++ b/infra/NEGOCIO.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>Key</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Fecha Venta</t>
   </si>
   <si>
-    <t>Requiere Reparación</t>
-  </si>
-  <si>
     <t>PROD-001</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
   </si>
   <si>
     <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>PROD-002</t>
@@ -225,7 +219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -283,126 +277,117 @@
       <c r="R1" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="0">
-        <v>18</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="D2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="E2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="F2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="G2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="H2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="H2" t="s" s="0">
-        <v>26</v>
-      </c>
       <c r="I2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="J2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s" s="0">
+      <c r="L2" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="M2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="N2" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="O2" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="P2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="Q2" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="Q2" t="s" s="0">
-        <v>34</v>
-      </c>
       <c r="R2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s" s="0">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="D3" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="F3" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="G3" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="F3" t="s" s="0">
+      <c r="H3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="G3" t="s" s="0">
+      <c r="L3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="H3" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s" s="0">
+      <c r="M3" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="N3" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="M3" t="s" s="0">
+      <c r="O3" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="N3" t="s" s="0">
+      <c r="P3" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="O3" t="s" s="0">
+      <c r="Q3" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="P3" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="Q3" t="s" s="0">
-        <v>49</v>
-      </c>
       <c r="R3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="S3" t="s" s="0">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -417,35 +402,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>50</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
